--- a/Sindhi Muslim/Petty Cash/Petty Cash.xlsx
+++ b/Sindhi Muslim/Petty Cash/Petty Cash.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Petty Cash\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB643696-CC5C-4514-9BFD-B50EE59AAD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7D3CF2-DF3D-4077-89F7-9C5B6D670C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{231916D2-A292-407F-8A31-C10D6447FE4F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{231916D2-A292-407F-8A31-C10D6447FE4F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
   <si>
     <t>S No</t>
   </si>
@@ -75,9 +76,6 @@
     <t>Water Tankers (3 Tankers)</t>
   </si>
   <si>
-    <t>Bismillah Paper Mart</t>
-  </si>
-  <si>
     <t>Stationary</t>
   </si>
   <si>
@@ -103,6 +101,9 @@
   </si>
   <si>
     <t>Syeda Samiya Kazmi</t>
+  </si>
+  <si>
+    <t>MashaAllah Paper Mart</t>
   </si>
 </sst>
 </file>
@@ -110,7 +111,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -348,29 +349,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -378,7 +360,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -414,6 +396,49 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,180 +753,401 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF07BA9-249D-46E3-BF1A-38868902D85E}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
+      <c r="A3" s="2"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="27">
+        <v>1</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="29">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="27">
+        <v>2</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="29">
+        <v>15700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="27">
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="29">
+        <v>21985</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="31">
+        <f>SUM(D5:D8)</f>
+        <v>42445</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="6">
+        <f ca="1">TODAY()</f>
+        <v>45590</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="20"/>
+    </row>
+    <row r="29" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="23"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="27">
+        <v>1</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="29">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="27">
+        <v>2</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="29">
+        <v>6830</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="27">
+        <v>3</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="29">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="11"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="13"/>
+    </row>
+    <row r="36" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="31">
+        <f>SUM(D32:D35)</f>
+        <v>28830</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="B41" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B42" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B43" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B44" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="B45" s="6">
+        <f ca="1">TODAY()</f>
+        <v>45590</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A29:D29"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83492EA8-036A-461F-922D-B9CF4AE3784F}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
+    </row>
+    <row r="2" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="18">
-        <v>1</v>
-      </c>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="13">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="13">
+        <v>6830</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="B7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="13">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="17">
+        <f>SUM(D5:D8)</f>
+        <v>28830</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="20">
-        <v>4760</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
-        <v>2</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="20">
-        <v>15700</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
-        <v>3</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="20">
-        <v>21985</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
-        <v>4</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="20">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
-        <v>5</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="20">
-        <v>6830</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
-        <v>6</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="20">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="24">
-        <f>SUM(D5:D11)</f>
-        <v>71275</v>
+    </row>
+    <row r="15" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="14" t="s">
-        <v>19</v>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="13">
+      <c r="B18" s="6">
         <f ca="1">TODAY()</f>
-        <v>45589</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>45590</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
